--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136968608</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136968612</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136968614</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136968617</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136969706</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136969707</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136968610</v>
       </c>
       <c r="B13" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136968608</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136968612</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136968614</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136968617</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136969706</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136969707</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136968610</v>
       </c>
       <c r="B13" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136968608</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136968612</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136968614</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136968617</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136969706</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136969707</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136968610</v>
       </c>
       <c r="B13" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136968608</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136968612</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136968614</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136968617</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136969706</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136969707</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136968610</v>
       </c>
       <c r="B13" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136968608</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136968612</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136968614</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136968617</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136969706</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136969707</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136968610</v>
       </c>
       <c r="B13" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,48 +1255,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136968608</v>
+        <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>80617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NV Korpimäki, Dlr</t>
+          <t>Jomtlamm, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481551</v>
+        <v>481417</v>
       </c>
       <c r="R7" t="n">
-        <v>6814569</v>
+        <v>6814689</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,22 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,27 +1340,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968608</t>
+          <t>https://artportalen.se/Sighting/137230096</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136968612</v>
+        <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481542</v>
+        <v>481551</v>
       </c>
       <c r="R8" t="n">
-        <v>6814577</v>
+        <v>6814569</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,16 +1463,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968612</t>
+          <t>https://artportalen.se/Sighting/136968608</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136968614</v>
+        <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481521</v>
+        <v>481542</v>
       </c>
       <c r="R9" t="n">
-        <v>6814582</v>
+        <v>6814577</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,16 +1575,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968614</t>
+          <t>https://artportalen.se/Sighting/136968612</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136968617</v>
+        <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481488</v>
+        <v>481521</v>
       </c>
       <c r="R10" t="n">
-        <v>6814585</v>
+        <v>6814582</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1661,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,16 +1687,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968617</t>
+          <t>https://artportalen.se/Sighting/136968614</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136969706</v>
+        <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481540</v>
+        <v>481488</v>
       </c>
       <c r="R11" t="n">
-        <v>6814591</v>
+        <v>6814585</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1773,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,46 +1784,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969706</t>
+          <t>https://artportalen.se/Sighting/136968617</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136969707</v>
+        <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481507</v>
+        <v>481540</v>
       </c>
       <c r="R12" t="n">
-        <v>6814615</v>
+        <v>6814591</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,17 +1899,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1951,38 +1926,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969707</t>
+          <t>https://artportalen.se/Sighting/136969706</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136968610</v>
+        <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79512</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,13 +1967,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481546</v>
+        <v>481507</v>
       </c>
       <c r="R13" t="n">
-        <v>6814573</v>
+        <v>6814615</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,74 +2023,84 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968610</t>
+          <t>https://artportalen.se/Sighting/136969707</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136969705</v>
+        <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NV Korpimäki, Dlr</t>
+          <t>Jomtlamm, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481540</v>
+        <v>481451</v>
       </c>
       <c r="R14" t="n">
-        <v>6814591</v>
+        <v>6814595</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2139,22 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,70 +2144,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969705</t>
+          <t>https://artportalen.se/Sighting/137230142</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136968618</v>
+        <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NV Korpimäki, Dlr</t>
+          <t>Jomtlamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481391</v>
+        <v>481432</v>
       </c>
       <c r="R15" t="n">
-        <v>6814648</v>
+        <v>6814604</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2256,27 +2226,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Få spår</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,18 +2246,583 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137230171</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136968610</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79525</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NV Korpimäki, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481546</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6814573</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136968610</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136969705</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58018</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NV Korpimäki, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481540</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6814591</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969705</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136968618</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NV Korpimäki, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481391</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6814648</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Få spår</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136968618</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137230157</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jomtlamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481432</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6814604</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137230157</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137230212</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jomtlamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481405</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6814612</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137230212</t>
         </is>
       </c>
     </row>
@@ -2322,6 +2842,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>136969705</v>
       </c>
       <c r="B17" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136968618</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>137230157</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137230212</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -2404,11 +2404,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Korpimäki, Dlr</t>
@@ -2521,11 +2517,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Korpimäki, Dlr</t>
@@ -2643,11 +2635,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jomtlamm, Dlr</t>
@@ -2750,11 +2738,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jomtlamm, Dlr</t>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>136969705</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136968618</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137230157</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137230212</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>136969705</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136968618</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137230157</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137230212</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>136969705</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136968618</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137230157</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137230212</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35597-2026 artfynd.xlsx
+++ b/artfynd/A 35597-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968611</v>
       </c>
       <c r="B2" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968613</v>
       </c>
       <c r="B3" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968615</v>
       </c>
       <c r="B4" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968616</v>
       </c>
       <c r="B5" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136969708</v>
       </c>
       <c r="B6" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137230096</v>
       </c>
       <c r="B7" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136968608</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136968612</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136968614</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136968617</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136969706</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136969707</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137230142</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137230171</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136968610</v>
       </c>
       <c r="B16" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>136969705</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136968618</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137230157</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137230212</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
